--- a/dist/sample/ccocr_test_plan_FILLED.xlsx
+++ b/dist/sample/ccocr_test_plan_FILLED.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cy/Desktop/CLAUDEs/ccocr/dist/sample/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E7F845-C3A7-8A44-8613-F75499FCD05A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F68F1762-7880-1140-A6B1-281B6A72E7AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="1300" windowWidth="36020" windowHeight="18860" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3660" yWindow="1180" windowWidth="36020" windowHeight="21120" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テスト計画" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="104">
   <si>
     <t>No.</t>
   </si>
@@ -187,6 +187,7 @@
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>/</t>
@@ -207,6 +208,7 @@
         <sz val="11"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="宋体"/>
+        <family val="3"/>
         <charset val="134"/>
       </rPr>
       <t>)</t>
@@ -512,6 +514,10 @@
     <t>[DONE]</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
+  <si>
+    <t>[python -u main.py で対処]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -530,17 +536,20 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -703,6 +712,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -711,7 +721,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1497,13 +1506,13 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="20" customHeight="1">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="14"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="15"/>
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" ht="112" customHeight="1">
@@ -1556,13 +1565,13 @@
       <c r="E5" s="3"/>
     </row>
     <row r="6" spans="1:6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="15"/>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="1:6" ht="55" customHeight="1">
@@ -1600,13 +1609,13 @@
       </c>
     </row>
     <row r="9" spans="1:6" ht="20" customHeight="1">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="15"/>
       <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6" ht="55" customHeight="1">
@@ -1704,13 +1713,13 @@
       <c r="E15" s="3"/>
     </row>
     <row r="16" spans="1:6" ht="20" customHeight="1">
-      <c r="A16" s="12" t="s">
+      <c r="A16" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="14"/>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="15"/>
       <c r="F16" s="2"/>
     </row>
     <row r="17" spans="1:6" ht="55" customHeight="1">
@@ -1794,13 +1803,13 @@
       <c r="E22" s="3"/>
     </row>
     <row r="23" spans="1:6" ht="20" customHeight="1">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="14"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="15"/>
       <c r="F23" s="2"/>
     </row>
     <row r="24" spans="1:6" ht="55" customHeight="1">
@@ -1878,10 +1887,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6">
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="15"/>
+      <c r="D2" s="16"/>
     </row>
     <row r="3" spans="2:6">
       <c r="C3" s="10" t="s">
@@ -1991,10 +2000,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6">
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="15"/>
+      <c r="D2" s="16"/>
     </row>
     <row r="3" spans="2:6">
       <c r="C3" s="10" t="s">
@@ -2080,7 +2089,7 @@
       <c r="B1" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="16" t="s">
+      <c r="M1" s="12" t="s">
         <v>102</v>
       </c>
     </row>
@@ -2089,15 +2098,18 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:20">
       <c r="A24">
         <v>2</v>
       </c>
       <c r="B24" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="60" spans="1:2">
+      <c r="T24" s="12" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22">
       <c r="A60">
         <v>3</v>
       </c>
@@ -2105,9 +2117,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:22">
       <c r="B61" t="s">
         <v>53</v>
+      </c>
+      <c r="V61" s="12" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="65" spans="15:15">

--- a/dist/sample/ccocr_test_plan_FILLED.xlsx
+++ b/dist/sample/ccocr_test_plan_FILLED.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cy/Desktop/CLAUDEs/ccocr/dist/sample/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{004D19BB-61D5-AD4E-A817-ACFB5419CE57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0430F6-5D58-6E4C-B558-D12839CEC91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8020" yWindow="1700" windowWidth="36020" windowHeight="21120" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3580" yWindow="1360" windowWidth="26520" windowHeight="18660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テスト計画" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="121">
   <si>
     <t>No.</t>
   </si>
@@ -242,6 +242,238 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>git pull が走る（コンソールに表示される）：OK
+設定Excelダイアログが開く：テスト計画の誤り</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>コンソールへのログ出力がスムースではなく、ある程度溜まってから一気に表示される</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ログファイルは正しく作成されているので、要解決 と言うことでは無いが、なぜ？？</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>この状態でしばらく動かない</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Flask の出力だけ、それ以前のログをすっ飛ばして出る</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>しばらく待ってみると、溜まったものが一気に出る</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>処理終わっても、まだログが出力されきっていない</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>古いログファイルの自動削除は実装すべき</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>利用者は ChuanlaiApps フォルダを意識する必要ないように作るべき</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>古いログを自動削除しないと、ディスクが枯渇する</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>１０世代か？？</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>関連して、Sentry を使った異常終了検知を考えている。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>input フォルダには設定エクセルがあるフォルダ内のファイルだけをcopyするように変更すべき</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>馬鹿でかいサブフォルダがあると、とんでも無いことになる。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>エクセルで"webとエクセルの両方で確認"を選択して処理し、web画面で修正を行うと、</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>_WEB.xlsm の出力エクセルは、修正が反映されるが、ミニ画像のあるエクセルは（当然だが）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>反映されない。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>正しい挙動だが、利用者には混乱を招くか？</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>"webとエクセルの両方で確認"は、メニューから省くか？</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>test 2 シートのスクショ参照</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>過去ログ再利用時：中身カラ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>テスト計画に誤り
+log/{jobid}/{jobid}.dump.db がある
+log/{jobid}/{jobid}.dump.xlsx もある</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChuanlaiApps/output/{jobid} は置き場所変更</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{設定エクセルのあった場所}/{jobid} とする</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChuanlaiApps の肥大を防ぐ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>利用者に ChuanlaiApps を意識させない</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>pngPRE</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>pngUP</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>pngROT</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>pngMK</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>pngRMK</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>過去ログ利用</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>カラ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>アリ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>してない</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>した</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>test 7 シート参照</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>IGNORED</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>jsnRAW</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>jsnRAW+</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>jsnRAW++</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>jsn4db</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>FLDなし</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>過去ログ利用した場合は、"フォルダなし"に変更</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>過去ログ利用した場合は、過去ログからのコピーになっているか？</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>過去ログ利用の場合は、JSN* フォルダ作らない</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>output/{jobid}/に
+{jobid}.xlsm
+{jobid}_WEB.xlsm
+IGNORED/*png　　　　その他気づき 8 も参照</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>2d は 200dpi の意味のはずで、これはエクセル上の default
+nd は デフォルト を意味しているとおもうが、claude が理解していない
+従い test 12 - 17 はこの通り行わず、適宜オプションを変えて実行したログを残す</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[DONE]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[python -u main.py で対処]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>IGNORED フォルダに出力されるのは赤枠青枠描画前のものか？</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>今のテストでは空白ページだけ</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[誤解 描画あった]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[未実施：Sentry用意したら実装]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>[DONE 省いた]</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <t>1 アイコンファイルに問題
 　</t>
@@ -263,7 +495,27 @@
         <charset val="134"/>
       </rPr>
       <t>そのほか気づき 参照
-2 コンソール画面は最小化で
+2 コンソール画面は最小化で　</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>[少し対応済み 一瞬コンソール出る]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
 3 初回起動時も設定Excel選択ダイアログ出る
 　</t>
     </r>
@@ -299,235 +551,46 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>git pull が走る（コンソールに表示される）：OK
-設定Excelダイアログが開く：テスト計画の誤り</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>コンソールへのログ出力がスムースではなく、ある程度溜まってから一気に表示される</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ログファイルは正しく作成されているので、要解決 と言うことでは無いが、なぜ？？</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>この状態でしばらく動かない</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Flask の出力だけ、それ以前のログをすっ飛ばして出る</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>しばらく待ってみると、溜まったものが一気に出る</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>処理終わっても、まだログが出力されきっていない</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>古いログファイルの自動削除は実装すべき</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>利用者は ChuanlaiApps フォルダを意識する必要ないように作るべき</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>古いログを自動削除しないと、ディスクが枯渇する</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>１０世代か？？</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>関連して、Sentry を使った異常終了検知を考えている。</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>input フォルダには設定エクセルがあるフォルダ内のファイルだけをcopyするように変更すべき</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>馬鹿でかいサブフォルダがあると、とんでも無いことになる。</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>エクセルで"webとエクセルの両方で確認"を選択して処理し、web画面で修正を行うと、</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>_WEB.xlsm の出力エクセルは、修正が反映されるが、ミニ画像のあるエクセルは（当然だが）</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>反映されない。</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>正しい挙動だが、利用者には混乱を招くか？</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>"webとエクセルの両方で確認"は、メニューから省くか？</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>test 2 シートのスクショ参照</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>-</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>過去ログ再利用時：中身カラ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>テスト計画に誤り
-log/{jobid}/{jobid}.dump.db がある
-log/{jobid}/{jobid}.dump.xlsx もある</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ChuanlaiApps/output/{jobid} は置き場所変更</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>{設定エクセルのあった場所}/{jobid} とする</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>ChuanlaiApps の肥大を防ぐ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>利用者に ChuanlaiApps を意識させない</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>pngPRE</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>pngUP</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>pngROT</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>pngMK</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>pngRMK</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>過去ログ利用</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>カラ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>アリ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>してない</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>した</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>test 7 シート参照</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>IGNORED</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>jsnRAW</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>jsnRAW+</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>jsnRAW++</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>jsn4db</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>FLDなし</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>過去ログ利用した場合は、"フォルダなし"に変更</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>過去ログ利用した場合は、過去ログからのコピーになっているか？</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>過去ログ利用の場合は、JSN* フォルダ作らない</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>output/{jobid}/に
-{jobid}.xlsm
-{jobid}_WEB.xlsm
-IGNORED/*png　　　　その他気づき 8 も参照</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>2d は 200dpi の意味のはずで、これはエクセル上の default
-nd は デフォルト を意味しているとおもうが、claude が理解していない
-従い test 12 - 17 はこの通り行わず、適宜オプションを変えて実行したログを残す</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>[DONE]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>[python -u main.py で対処]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>IGNORED フォルダに出力されるのは赤枠青枠描画前のものか？</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>今のテストでは空白ページだけ</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>[誤解 描画あった]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>[未実施：Sentry用意したら実装]</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>[DONE 省いた]</t>
+    <t>あ、そうか。。。</t>
+  </si>
+  <si>
+    <t>過去ログ利用する時は、赤枠青枠は書かないで、コピー元の過去ログフォルダからすでに書いたやつをコピーしてくればいいだけか。</t>
+  </si>
+  <si>
+    <t>もっと言えば、そもそも</t>
+  </si>
+  <si>
+    <t>jsn* も png* も、プログラム保守する人とか _dd シート作る人だけが必要なので、一般利用者には無縁。</t>
+  </si>
+  <si>
+    <t>ただ、そこまで踏み込むと ccocr.exe の他に ccocr_dev.exe も要る？とか話ややこしすぎるので、この点は今は割愛。</t>
+  </si>
+  <si>
+    <t>過去ログ利用の際の png* は以下のようにします。</t>
+  </si>
+  <si>
+    <t>フォルダを作らない</t>
+  </si>
+  <si>
+    <t>　pngUP</t>
+  </si>
+  <si>
+    <t>フォルダを作成（過去ログのものをコピー）</t>
+  </si>
+  <si>
+    <t>　pngPRE</t>
+  </si>
+  <si>
+    <t>　pngROT</t>
+  </si>
+  <si>
+    <t>　pngMK</t>
+  </si>
+  <si>
+    <t>　pngRMK</t>
+  </si>
+  <si>
+    <t>[以下で改修]</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -535,7 +598,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -611,6 +674,14 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1540,8 +1611,8 @@
       <c r="D3" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>50</v>
+      <c r="E3" s="3" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="55" customHeight="1">
@@ -1558,7 +1629,7 @@
         <v>44</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="55" customHeight="1">
@@ -1600,7 +1671,7 @@
         <v>44</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="55" customHeight="1">
@@ -1617,7 +1688,7 @@
         <v>44</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="20" customHeight="1">
@@ -1656,10 +1727,10 @@
         <v>19</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="55" customHeight="1">
@@ -1674,7 +1745,7 @@
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="55" customHeight="1">
@@ -1689,7 +1760,7 @@
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="55" customHeight="1">
@@ -1703,10 +1774,10 @@
         <v>25</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="55" customHeight="1">
@@ -1746,7 +1817,7 @@
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="55" customHeight="1">
@@ -1891,7 +1962,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3CD311C-71F3-B54E-9614-9689F129940F}">
-  <dimension ref="B2:F10"/>
+  <dimension ref="B2:F29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
@@ -1900,97 +1971,171 @@
   <sheetData>
     <row r="2" spans="2:6">
       <c r="C2" s="16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D2" s="16"/>
     </row>
     <row r="3" spans="2:6">
       <c r="C3" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>86</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="4" spans="2:6">
       <c r="B4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="2:6">
       <c r="B5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="2:6">
       <c r="B6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="2:6">
       <c r="B7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="2:6">
       <c r="B8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="2:6">
       <c r="B10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6">
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+    </row>
+    <row r="12" spans="2:6">
+      <c r="B12" s="12" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6">
+      <c r="B13" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6">
+      <c r="B14" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6">
+      <c r="B16" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2">
+      <c r="B17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2">
+      <c r="B20" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2">
+      <c r="B23" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -2004,79 +2149,82 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB77554E-C774-BA45-B3EB-2B6E07C41A31}">
-  <dimension ref="B2:F10"/>
+  <dimension ref="B2:J10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6">
+    <row r="2" spans="2:10">
       <c r="C2" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" s="16"/>
+    </row>
+    <row r="3" spans="2:10">
+      <c r="C3" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10">
+      <c r="B4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="D2" s="16"/>
-    </row>
-    <row r="3" spans="2:6">
-      <c r="C3" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6">
-      <c r="B4" t="s">
+      <c r="F4" t="s">
+        <v>96</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10">
+      <c r="B5" t="s">
         <v>90</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="D4" s="10" t="s">
+      <c r="C5" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="F4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6">
-      <c r="B5" t="s">
+      <c r="D5" s="10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10">
+      <c r="B6" t="s">
         <v>91</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6">
-      <c r="B6" t="s">
+      <c r="C6" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10">
+      <c r="B7" t="s">
         <v>92</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6">
-      <c r="B7" t="s">
+      <c r="C7" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6">
+    </row>
+    <row r="8" spans="2:10">
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
     </row>
-    <row r="10" spans="2:6">
+    <row r="10" spans="2:10">
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
     </row>
@@ -2102,7 +2250,7 @@
         <v>41</v>
       </c>
       <c r="M1" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -2118,7 +2266,7 @@
         <v>45</v>
       </c>
       <c r="T24" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="60" spans="1:22">
@@ -2126,35 +2274,35 @@
         <v>3</v>
       </c>
       <c r="B60" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="61" spans="1:22">
       <c r="B61" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V61" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="65" spans="15:15">
       <c r="O65" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="124" spans="25:25">
       <c r="Y124" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="136" spans="29:29">
       <c r="AC136" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="164" spans="30:30">
       <c r="AD164" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="177" spans="1:17">
@@ -2162,33 +2310,33 @@
         <v>4</v>
       </c>
       <c r="B177" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="178" spans="1:17">
       <c r="B178" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="179" spans="1:17">
       <c r="B179" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="180" spans="1:17">
       <c r="B180" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F180" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="182" spans="1:17">
       <c r="B182" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="O182" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="184" spans="1:17" s="9" customFormat="1">
@@ -2196,15 +2344,15 @@
         <v>5</v>
       </c>
       <c r="B184" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="185" spans="1:17">
       <c r="B185" t="s">
+        <v>102</v>
+      </c>
+      <c r="J185" s="12" t="s">
         <v>103</v>
-      </c>
-      <c r="J185" s="12" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="187" spans="1:17">
@@ -2212,15 +2360,15 @@
         <v>6</v>
       </c>
       <c r="B187" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="188" spans="1:17">
       <c r="B188" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Q188" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="190" spans="1:17">
@@ -2228,30 +2376,30 @@
         <v>7</v>
       </c>
       <c r="B190" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="191" spans="1:17">
       <c r="B191" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="192" spans="1:17">
       <c r="B192" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="193" spans="1:16">
       <c r="B193" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="194" spans="1:16">
       <c r="B194" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P194" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="196" spans="1:16">
@@ -2259,15 +2407,15 @@
         <v>8</v>
       </c>
       <c r="B196" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N196" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="197" spans="1:16">
       <c r="B197" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -2275,7 +2423,7 @@
         <v>1</v>
       </c>
       <c r="C198" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -2283,7 +2431,7 @@
         <v>2</v>
       </c>
       <c r="C199" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
